--- a/Document/SoC_Design.xlsx
+++ b/Document/SoC_Design.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\SoC_Design\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B9F66F2-0A02-4CFD-9B81-0DFBBD3718D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{781CF6C3-0461-413F-958D-4426FA510AE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{813C5046-60F0-40FF-AAC7-48B46C31F73B}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{813C5046-60F0-40FF-AAC7-48B46C31F73B}"/>
   </bookViews>
   <sheets>
     <sheet name="TASK" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="35">
   <si>
     <t>No</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -173,6 +173,15 @@
   <si>
     <t>rd 레지스터 및 reg_wdata를 가지고 있어야함
 최소 2,3개 버퍼를 둬야할듯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>regdst_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 생각해보니 ex 단계에서 만들어서 bridge로 output만 넘겨주면 되는 걸 굳이 wb mux, mem mux 만들었음
+추후에 전면 수정 할것</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -309,11 +318,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1239,17 +1248,23 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="11" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B6" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+    <row r="6" spans="2:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="B6" s="1">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.3">
@@ -1353,26 +1368,26 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11" t="s">
+      <c r="C3" s="12"/>
+      <c r="D3" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B4" s="6">

--- a/Document/SoC_Design.xlsx
+++ b/Document/SoC_Design.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\SoC_Design\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{781CF6C3-0461-413F-958D-4426FA510AE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1842B30-2B80-46C9-9EAC-D0188436A62F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{813C5046-60F0-40FF-AAC7-48B46C31F73B}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="2" xr2:uid="{813C5046-60F0-40FF-AAC7-48B46C31F73B}"/>
   </bookViews>
   <sheets>
     <sheet name="TASK" sheetId="1" r:id="rId1"/>
     <sheet name="오류사항분석" sheetId="2" r:id="rId2"/>
-    <sheet name="교안참고" sheetId="3" r:id="rId3"/>
+    <sheet name="MemoryMap" sheetId="4" r:id="rId3"/>
+    <sheet name="교안참고" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="70">
   <si>
     <t>No</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -182,6 +183,146 @@
   <si>
     <t xml:space="preserve"> 생각해보니 ex 단계에서 만들어서 bridge로 output만 넘겨주면 되는 걸 굳이 wb mux, mem mux 만들었음
 추후에 전면 수정 할것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SRAM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GPIO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TIMER</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UART</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SPI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DMA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Interrupt Controller</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Device</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BOOT ROM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DDR Controller</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ADDR RANGE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I2C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x0000_0000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x0000_FFFF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x00D0_A000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x00D0_AFFF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x00D0_B000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x00D0_BFFF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x00D0_C000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x00D0_CFFF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x00D0_D000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x00D0_DFFF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x00D0_E000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x00D_0EFFF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AXI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>APB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AHB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TBD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x1000_0000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x1000_FFFF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x2000_0000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x2FFFF_FFFF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0xFFFF_FFFF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x3000_0000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -284,7 +425,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -322,6 +463,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1358,6 +1502,178 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12F42033-4B4E-4A2A-B38E-DB6853B9FE63}">
+  <dimension ref="B2:E12"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="2.625" customWidth="1"/>
+    <col min="2" max="2" width="18.625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="12.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" s="13"/>
+      <c r="E2" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B11" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C2:D2"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5803618C-83C4-4D14-8C32-40AC543E5199}">
   <dimension ref="B2:G8"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
